--- a/回後買上漲圖表_20260611/回後買上漲_嚴格版(1+2+3)_20260611.xlsx
+++ b/回後買上漲圖表_20260611/回後買上漲_嚴格版(1+2+3)_20260611.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -561,28 +561,28 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5410.TWO</t>
+          <t>2348.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>國眾</t>
+          <t>海悅</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>44.15</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>40.85</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>6520</v>
+        <v>5857</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>793</v>
+        <v>425</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -603,28 +603,28 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>6469.TWO</t>
+          <t>2913.TW</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>農林</t>
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>76.90000000000001</v>
+        <v>11.45</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>76</v>
+        <v>11.15</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>2013</v>
+        <v>12401</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>514</v>
+        <v>1479</v>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
@@ -637,6 +637,90 @@
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6186.TWO</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>新潤</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3498</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>697</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>6180.TWO</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>橘子</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>2457</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>924</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -646,6 +730,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
